--- a/outputs/50971.xlsx
+++ b/outputs/50971.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">COLLM</t>
   </si>
@@ -43,46 +43,46 @@
     <t xml:space="preserve">AL2231</t>
   </si>
   <si>
+    <t xml:space="preserve">AL2232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL2233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL2234</t>
+  </si>
+  <si>
     <t xml:space="preserve">AL2235</t>
   </si>
   <si>
+    <t xml:space="preserve">AL2236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL2237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL2238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL2239</t>
+  </si>
+  <si>
     <t xml:space="preserve">AL2240</t>
   </si>
   <si>
-    <t xml:space="preserve">AL2232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2239</t>
+    <t xml:space="preserve">AL2241</t>
   </si>
   <si>
     <t xml:space="preserve">AL2242</t>
   </si>
   <si>
+    <t xml:space="preserve">AL2243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL2244</t>
+  </si>
+  <si>
     <t xml:space="preserve">AL2245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2244</t>
   </si>
   <si>
     <t xml:space="preserve">AL2246</t>
@@ -178,20 +178,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -389,26 +393,26 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="20.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="20.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
@@ -417,10 +421,10 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -431,23 +435,29 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F3)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="2" t="n">
         <f aca="false" t="array" ref="F3:F13">_xlfn.UNIQUE(A2:A19)</f>
         <v>1005</v>
       </c>
       <c r="G3" s="1" t="str">
-        <f aca="false">INDEX($B$2:$B$19, MATCH(F3, $A$2:$A$19, 0))</f>
+        <f aca="false" t="array" ref="G3:K3">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F3,ROW($A$2:$A$19)-1),1)),"")</f>
         <v>AL2230</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>8</v>
+      <c r="H3" s="1" t="str">
+        <v>AL2230</v>
+      </c>
+      <c r="I3" s="1" t="str">
+        <v>AL2230</v>
+      </c>
+      <c r="J3" s="2" t="str">
+        <v>AL2230</v>
+      </c>
+      <c r="K3" s="2" t="str">
+        <v>AL2230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -455,17 +465,29 @@
         <v>1007</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F4)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="2" t="n">
         <v>1006</v>
       </c>
       <c r="G4" s="1" t="str">
-        <f aca="false">INDEX($B$2:$B$19, MATCH(F4, $A$2:$A$19, 0))</f>
+        <f aca="false" t="array" ref="G4:K4">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F4,ROW($A$2:$A$19)-1),1)),"")</f>
+        <v>AL2231</v>
+      </c>
+      <c r="H4" s="2" t="str">
+        <v>AL2231</v>
+      </c>
+      <c r="I4" s="2" t="str">
+        <v>AL2231</v>
+      </c>
+      <c r="J4" s="2" t="str">
+        <v>AL2231</v>
+      </c>
+      <c r="K4" s="2" t="str">
         <v>AL2231</v>
       </c>
     </row>
@@ -474,17 +496,29 @@
         <v>1008</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F5)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="2" t="n">
         <v>1007</v>
       </c>
       <c r="G5" s="1" t="str">
-        <f aca="false">INDEX($B$2:$B$19, MATCH(F5, $A$2:$A$19, 0))</f>
+        <f aca="false" t="array" ref="G5:K5">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F5,ROW($A$2:$A$19)-1),1)),"")</f>
+        <v>AL2232</v>
+      </c>
+      <c r="H5" s="2" t="str">
+        <v>AL2232</v>
+      </c>
+      <c r="I5" s="2" t="str">
+        <v>AL2232</v>
+      </c>
+      <c r="J5" s="2" t="str">
+        <v>AL2232</v>
+      </c>
+      <c r="K5" s="2" t="str">
         <v>AL2232</v>
       </c>
     </row>
@@ -493,30 +527,30 @@
         <v>1009</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F6)</f>
         <v>5</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="2" t="n">
         <v>1008</v>
       </c>
       <c r="G6" s="1" t="str">
-        <f aca="false">INDEX($B$2:$B$19, MATCH(F6, $A$2:$A$19, 0))</f>
+        <f aca="false" t="array" ref="G6:K6">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F6,ROW($A$2:$A$19)-1),1)),"")</f>
         <v>AL2233</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>15</v>
+      <c r="H6" s="1" t="str">
+        <v>AL2233</v>
+      </c>
+      <c r="I6" s="1" t="str">
+        <v>AL2233</v>
+      </c>
+      <c r="J6" s="1" t="str">
+        <v>AL2233</v>
+      </c>
+      <c r="K6" s="1" t="str">
+        <v>AL2233</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -524,17 +558,29 @@
         <v>1005</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F7)</f>
         <v>1</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="2" t="n">
         <v>1009</v>
       </c>
       <c r="G7" s="1" t="str">
-        <f aca="false">INDEX($B$2:$B$19, MATCH(F7, $A$2:$A$19, 0))</f>
+        <f aca="false" t="array" ref="G7:K7">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F7,ROW($A$2:$A$19)-1),1)),"")</f>
+        <v>AL2234</v>
+      </c>
+      <c r="H7" s="2" t="str">
+        <v>AL2234</v>
+      </c>
+      <c r="I7" s="2" t="str">
+        <v>AL2234</v>
+      </c>
+      <c r="J7" s="2" t="str">
+        <v>AL2234</v>
+      </c>
+      <c r="K7" s="2" t="str">
         <v>AL2234</v>
       </c>
     </row>
@@ -543,17 +589,29 @@
         <v>1008</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F8)</f>
         <v>1</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="2" t="n">
         <v>1125</v>
       </c>
       <c r="G8" s="1" t="str">
-        <f aca="false">INDEX($B$2:$B$19, MATCH(F8, $A$2:$A$19, 0))</f>
+        <f aca="false" t="array" ref="G8:K8">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F8,ROW($A$2:$A$19)-1),1)),"")</f>
+        <v>AL2237</v>
+      </c>
+      <c r="H8" s="2" t="str">
+        <v>AL2237</v>
+      </c>
+      <c r="I8" s="2" t="str">
+        <v>AL2237</v>
+      </c>
+      <c r="J8" s="2" t="str">
+        <v>AL2237</v>
+      </c>
+      <c r="K8" s="2" t="str">
         <v>AL2237</v>
       </c>
     </row>
@@ -562,17 +620,29 @@
         <v>1125</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F9)</f>
         <v>1</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="2" t="n">
         <v>1256</v>
       </c>
       <c r="G9" s="1" t="str">
-        <f aca="false">INDEX($B$2:$B$19, MATCH(F9, $A$2:$A$19, 0))</f>
+        <f aca="false" t="array" ref="G9:K9">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F9,ROW($A$2:$A$19)-1),1)),"")</f>
+        <v>AL2238</v>
+      </c>
+      <c r="H9" s="2" t="str">
+        <v>AL2238</v>
+      </c>
+      <c r="I9" s="2" t="str">
+        <v>AL2238</v>
+      </c>
+      <c r="J9" s="2" t="str">
+        <v>AL2238</v>
+      </c>
+      <c r="K9" s="2" t="str">
         <v>AL2238</v>
       </c>
     </row>
@@ -581,17 +651,29 @@
         <v>1256</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F10)</f>
         <v>1</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="2" t="n">
         <v>1120</v>
       </c>
       <c r="G10" s="1" t="str">
-        <f aca="false">INDEX($B$2:$B$19, MATCH(F10, $A$2:$A$19, 0))</f>
+        <f aca="false" t="array" ref="G10:K10">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F10,ROW($A$2:$A$19)-1),1)),"")</f>
+        <v>AL2241</v>
+      </c>
+      <c r="H10" s="2" t="str">
+        <v>AL2241</v>
+      </c>
+      <c r="I10" s="2" t="str">
+        <v>AL2241</v>
+      </c>
+      <c r="J10" s="2" t="str">
+        <v>AL2241</v>
+      </c>
+      <c r="K10" s="2" t="str">
         <v>AL2241</v>
       </c>
     </row>
@@ -600,37 +682,60 @@
         <v>1008</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F11)</f>
         <v>2</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="2" t="n">
         <v>1100</v>
       </c>
       <c r="G11" s="1" t="str">
-        <f aca="false">INDEX($B$2:$B$19, MATCH(F11, $A$2:$A$19, 0))</f>
+        <f aca="false" t="array" ref="G11:K11">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F11,ROW($A$2:$A$19)-1),1)),"")</f>
         <v>AL2243</v>
       </c>
-      <c r="H11" s="1"/>
+      <c r="H11" s="1" t="str">
+        <v>AL2243</v>
+      </c>
+      <c r="I11" s="2" t="str">
+        <v>AL2243</v>
+      </c>
+      <c r="J11" s="2" t="str">
+        <v>AL2243</v>
+      </c>
+      <c r="K11" s="2" t="str">
+        <v>AL2243</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>1005</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F12)</f>
         <v>1</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="2" t="n">
         <v>1369</v>
       </c>
       <c r="G12" s="1" t="str">
-        <f aca="false">INDEX($B$2:$B$19, MATCH(F12, $A$2:$A$19, 0))</f>
+        <f aca="false" t="array" ref="G12:K12">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F12,ROW($A$2:$A$19)-1),1)),"")</f>
+        <v>AL2244</v>
+      </c>
+      <c r="H12" s="2" t="str">
+        <v>AL2244</v>
+      </c>
+      <c r="I12" s="2" t="str">
+        <v>AL2244</v>
+      </c>
+      <c r="J12" s="2" t="str">
+        <v>AL2244</v>
+      </c>
+      <c r="K12" s="2" t="str">
         <v>AL2244</v>
       </c>
     </row>
@@ -639,17 +744,29 @@
         <v>1120</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F13)</f>
         <v>1</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="2" t="n">
         <v>5223</v>
       </c>
       <c r="G13" s="1" t="str">
-        <f aca="false">INDEX($B$2:$B$19, MATCH(F13, $A$2:$A$19, 0))</f>
+        <f aca="false" t="array" ref="G13:K13">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F13,ROW($A$2:$A$19)-1),1)),"")</f>
+        <v>AL2246</v>
+      </c>
+      <c r="H13" s="2" t="str">
+        <v>AL2246</v>
+      </c>
+      <c r="I13" s="2" t="str">
+        <v>AL2246</v>
+      </c>
+      <c r="J13" s="2" t="str">
+        <v>AL2246</v>
+      </c>
+      <c r="K13" s="2" t="str">
         <v>AL2246</v>
       </c>
     </row>
@@ -658,7 +775,7 @@
         <v>1008</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -666,7 +783,7 @@
         <v>1100</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -674,7 +791,7 @@
         <v>1369</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -682,7 +799,7 @@
         <v>1008</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/outputs/50971.xlsx
+++ b/outputs/50971.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
   <si>
     <t xml:space="preserve">COLLM</t>
   </si>
@@ -43,6 +43,12 @@
     <t xml:space="preserve">AL2231</t>
   </si>
   <si>
+    <t xml:space="preserve">AL2235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL2240</t>
+  </si>
+  <si>
     <t xml:space="preserve">AL2232</t>
   </si>
   <si>
@@ -52,40 +58,40 @@
     <t xml:space="preserve">AL2234</t>
   </si>
   <si>
-    <t xml:space="preserve">AL2235</t>
+    <t xml:space="preserve">AL2236,AL2239,AL2242,AL2245</t>
   </si>
   <si>
     <t xml:space="preserve">AL2236</t>
   </si>
   <si>
+    <t xml:space="preserve">AL2239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL2242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL2245</t>
+  </si>
+  <si>
     <t xml:space="preserve">AL2237</t>
   </si>
   <si>
     <t xml:space="preserve">AL2238</t>
   </si>
   <si>
-    <t xml:space="preserve">AL2239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2240</t>
-  </si>
-  <si>
     <t xml:space="preserve">AL2241</t>
   </si>
   <si>
-    <t xml:space="preserve">AL2242</t>
+    <t xml:space="preserve">AL2243,AL2247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL2244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL2246</t>
   </si>
   <si>
     <t xml:space="preserve">AL2243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL2246</t>
   </si>
   <si>
     <t xml:space="preserve">AL2247</t>
@@ -443,21 +449,14 @@
         <f aca="false" t="array" ref="F3:F13">_xlfn.UNIQUE(A2:A19)</f>
         <v>1005</v>
       </c>
-      <c r="G3" s="1" t="str">
-        <f aca="false" t="array" ref="G3:K3">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F3,ROW($A$2:$A$19)-1),1)),"")</f>
-        <v>AL2230</v>
-      </c>
-      <c r="H3" s="1" t="str">
-        <v>AL2230</v>
-      </c>
-      <c r="I3" s="1" t="str">
-        <v>AL2230</v>
-      </c>
-      <c r="J3" s="2" t="str">
-        <v>AL2230</v>
-      </c>
-      <c r="K3" s="2" t="str">
-        <v>AL2230</v>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -465,7 +464,7 @@
         <v>1007</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F4)</f>
@@ -474,21 +473,8 @@
       <c r="F4" s="2" t="n">
         <v>1006</v>
       </c>
-      <c r="G4" s="1" t="str">
-        <f aca="false" t="array" ref="G4:K4">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F4,ROW($A$2:$A$19)-1),1)),"")</f>
-        <v>AL2231</v>
-      </c>
-      <c r="H4" s="2" t="str">
-        <v>AL2231</v>
-      </c>
-      <c r="I4" s="2" t="str">
-        <v>AL2231</v>
-      </c>
-      <c r="J4" s="2" t="str">
-        <v>AL2231</v>
-      </c>
-      <c r="K4" s="2" t="str">
-        <v>AL2231</v>
+      <c r="G4" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -496,7 +482,7 @@
         <v>1008</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F5)</f>
@@ -505,21 +491,8 @@
       <c r="F5" s="2" t="n">
         <v>1007</v>
       </c>
-      <c r="G5" s="1" t="str">
-        <f aca="false" t="array" ref="G5:K5">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F5,ROW($A$2:$A$19)-1),1)),"")</f>
-        <v>AL2232</v>
-      </c>
-      <c r="H5" s="2" t="str">
-        <v>AL2232</v>
-      </c>
-      <c r="I5" s="2" t="str">
-        <v>AL2232</v>
-      </c>
-      <c r="J5" s="2" t="str">
-        <v>AL2232</v>
-      </c>
-      <c r="K5" s="2" t="str">
-        <v>AL2232</v>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -527,7 +500,7 @@
         <v>1009</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F6)</f>
@@ -536,21 +509,20 @@
       <c r="F6" s="2" t="n">
         <v>1008</v>
       </c>
-      <c r="G6" s="1" t="str">
-        <f aca="false" t="array" ref="G6:K6">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F6,ROW($A$2:$A$19)-1),1)),"")</f>
-        <v>AL2233</v>
-      </c>
-      <c r="H6" s="1" t="str">
-        <v>AL2233</v>
-      </c>
-      <c r="I6" s="1" t="str">
-        <v>AL2233</v>
-      </c>
-      <c r="J6" s="1" t="str">
-        <v>AL2233</v>
-      </c>
-      <c r="K6" s="1" t="str">
-        <v>AL2233</v>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -558,7 +530,7 @@
         <v>1005</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F7)</f>
@@ -567,21 +539,8 @@
       <c r="F7" s="2" t="n">
         <v>1009</v>
       </c>
-      <c r="G7" s="1" t="str">
-        <f aca="false" t="array" ref="G7:K7">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F7,ROW($A$2:$A$19)-1),1)),"")</f>
-        <v>AL2234</v>
-      </c>
-      <c r="H7" s="2" t="str">
-        <v>AL2234</v>
-      </c>
-      <c r="I7" s="2" t="str">
-        <v>AL2234</v>
-      </c>
-      <c r="J7" s="2" t="str">
-        <v>AL2234</v>
-      </c>
-      <c r="K7" s="2" t="str">
-        <v>AL2234</v>
+      <c r="G7" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -589,7 +548,7 @@
         <v>1008</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F8)</f>
@@ -598,21 +557,8 @@
       <c r="F8" s="2" t="n">
         <v>1125</v>
       </c>
-      <c r="G8" s="1" t="str">
-        <f aca="false" t="array" ref="G8:K8">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F8,ROW($A$2:$A$19)-1),1)),"")</f>
-        <v>AL2237</v>
-      </c>
-      <c r="H8" s="2" t="str">
-        <v>AL2237</v>
-      </c>
-      <c r="I8" s="2" t="str">
-        <v>AL2237</v>
-      </c>
-      <c r="J8" s="2" t="str">
-        <v>AL2237</v>
-      </c>
-      <c r="K8" s="2" t="str">
-        <v>AL2237</v>
+      <c r="G8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -620,7 +566,7 @@
         <v>1125</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E9" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F9)</f>
@@ -629,21 +575,8 @@
       <c r="F9" s="2" t="n">
         <v>1256</v>
       </c>
-      <c r="G9" s="1" t="str">
-        <f aca="false" t="array" ref="G9:K9">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F9,ROW($A$2:$A$19)-1),1)),"")</f>
-        <v>AL2238</v>
-      </c>
-      <c r="H9" s="2" t="str">
-        <v>AL2238</v>
-      </c>
-      <c r="I9" s="2" t="str">
-        <v>AL2238</v>
-      </c>
-      <c r="J9" s="2" t="str">
-        <v>AL2238</v>
-      </c>
-      <c r="K9" s="2" t="str">
-        <v>AL2238</v>
+      <c r="G9" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -651,7 +584,7 @@
         <v>1256</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F10)</f>
@@ -660,21 +593,8 @@
       <c r="F10" s="2" t="n">
         <v>1120</v>
       </c>
-      <c r="G10" s="1" t="str">
-        <f aca="false" t="array" ref="G10:K10">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F10,ROW($A$2:$A$19)-1),1)),"")</f>
-        <v>AL2241</v>
-      </c>
-      <c r="H10" s="2" t="str">
-        <v>AL2241</v>
-      </c>
-      <c r="I10" s="2" t="str">
-        <v>AL2241</v>
-      </c>
-      <c r="J10" s="2" t="str">
-        <v>AL2241</v>
-      </c>
-      <c r="K10" s="2" t="str">
-        <v>AL2241</v>
+      <c r="G10" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -691,29 +611,17 @@
       <c r="F11" s="2" t="n">
         <v>1100</v>
       </c>
-      <c r="G11" s="1" t="str">
-        <f aca="false" t="array" ref="G11:K11">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F11,ROW($A$2:$A$19)-1),1)),"")</f>
-        <v>AL2243</v>
-      </c>
-      <c r="H11" s="1" t="str">
-        <v>AL2243</v>
-      </c>
-      <c r="I11" s="2" t="str">
-        <v>AL2243</v>
-      </c>
-      <c r="J11" s="2" t="str">
-        <v>AL2243</v>
-      </c>
-      <c r="K11" s="2" t="str">
-        <v>AL2243</v>
-      </c>
+      <c r="G11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>1005</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E12" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F12)</f>
@@ -722,21 +630,8 @@
       <c r="F12" s="2" t="n">
         <v>1369</v>
       </c>
-      <c r="G12" s="1" t="str">
-        <f aca="false" t="array" ref="G12:K12">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F12,ROW($A$2:$A$19)-1),1)),"")</f>
-        <v>AL2244</v>
-      </c>
-      <c r="H12" s="2" t="str">
-        <v>AL2244</v>
-      </c>
-      <c r="I12" s="2" t="str">
-        <v>AL2244</v>
-      </c>
-      <c r="J12" s="2" t="str">
-        <v>AL2244</v>
-      </c>
-      <c r="K12" s="2" t="str">
-        <v>AL2244</v>
+      <c r="G12" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -744,7 +639,7 @@
         <v>1120</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E13" s="3" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,F13)</f>
@@ -753,21 +648,8 @@
       <c r="F13" s="2" t="n">
         <v>5223</v>
       </c>
-      <c r="G13" s="1" t="str">
-        <f aca="false" t="array" ref="G13:K13">IFERROR(INDEX($B$2:$B$19,SMALL(IF($A$2:$A$19=F13,ROW($A$2:$A$19)-1),1)),"")</f>
-        <v>AL2246</v>
-      </c>
-      <c r="H13" s="2" t="str">
-        <v>AL2246</v>
-      </c>
-      <c r="I13" s="2" t="str">
-        <v>AL2246</v>
-      </c>
-      <c r="J13" s="2" t="str">
-        <v>AL2246</v>
-      </c>
-      <c r="K13" s="2" t="str">
-        <v>AL2246</v>
+      <c r="G13" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -775,7 +657,7 @@
         <v>1008</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -783,7 +665,7 @@
         <v>1100</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -791,7 +673,7 @@
         <v>1369</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -799,7 +681,7 @@
         <v>1008</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -807,7 +689,7 @@
         <v>5223</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -815,7 +697,7 @@
         <v>1100</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
